--- a/public/plantilla-cal-maestro.xlsx
+++ b/public/plantilla-cal-maestro.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listado Maestro" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="165" formatCode="#,##0.##"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="#,##0.##"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="hh:mm"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -637,7 +637,7 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -725,34 +725,34 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -926,70 +926,70 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -1063,7 +1063,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1102,11 +1102,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -11402,32 +11402,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>2252203</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>177646</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>2252203</colOff>
+      <row>7</row>
+      <rowOff>177646</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3564000" cy="1692000"/>
@@ -11438,11 +11438,11 @@
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11744,9 +11744,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="4" tint="0.3999755851924192"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="67" min="1" max="1"/>
@@ -12682,166 +12683,252 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="22.05" customHeight="1" s="67">
+    <row r="31" ht="29" customHeight="1" s="67">
       <c r="A31" s="116" t="n">
         <v>17</v>
       </c>
-      <c r="B31" s="161" t="n"/>
-      <c r="C31" s="161" t="n"/>
-      <c r="D31" s="161" t="n"/>
-      <c r="E31" s="161" t="n"/>
-      <c r="F31" s="161" t="n"/>
-      <c r="G31" s="161" t="n"/>
-      <c r="H31" s="167" t="n"/>
-      <c r="I31" s="167" t="n"/>
+      <c r="B31" s="166" t="inlineStr">
+        <is>
+          <t>RYR-CA-017</t>
+        </is>
+      </c>
+      <c r="C31" s="166" t="inlineStr">
+        <is>
+          <t>Informe Mensual de Calidad</t>
+        </is>
+      </c>
+      <c r="D31" s="166" t="inlineStr">
+        <is>
+          <t>Ingeniero de calidad</t>
+        </is>
+      </c>
+      <c r="E31" s="166" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="F31" s="166" t="inlineStr">
+        <is>
+          <t>Carpeta de calidad y app</t>
+        </is>
+      </c>
+      <c r="G31" s="166" t="inlineStr">
+        <is>
+          <t>Cierre del contrato + 5 años</t>
+        </is>
+      </c>
+      <c r="H31" s="116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="116" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
     </row>
-    <row r="32" ht="19.95" customHeight="1" s="67">
-      <c r="A32" s="108" t="inlineStr">
+    <row r="32" ht="29" customHeight="1" s="67">
+      <c r="A32" s="116" t="n">
+        <v>18</v>
+      </c>
+      <c r="B32" s="166" t="inlineStr">
+        <is>
+          <t>RYR-CA-018</t>
+        </is>
+      </c>
+      <c r="C32" s="166" t="inlineStr">
+        <is>
+          <t>Equipos de Medición y Laboratorio</t>
+        </is>
+      </c>
+      <c r="D32" s="166" t="inlineStr">
+        <is>
+          <t>Ingeniero de calidad</t>
+        </is>
+      </c>
+      <c r="E32" s="166" t="inlineStr">
+        <is>
+          <t>Al calibrar o ingresar cada equipo</t>
+        </is>
+      </c>
+      <c r="F32" s="166" t="inlineStr">
+        <is>
+          <t>Carpeta de calidad y app</t>
+        </is>
+      </c>
+      <c r="G32" s="166" t="inlineStr">
+        <is>
+          <t>Cierre del contrato + 5 años</t>
+        </is>
+      </c>
+      <c r="H32" s="116" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="116" t="inlineStr">
+        <is>
+          <t>Vigente</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22.05" customHeight="1" s="67">
+      <c r="A33" s="116" t="n">
+        <v>19</v>
+      </c>
+      <c r="B33" s="161" t="n"/>
+      <c r="C33" s="161" t="n"/>
+      <c r="D33" s="161" t="n"/>
+      <c r="E33" s="161" t="n"/>
+      <c r="F33" s="161" t="n"/>
+      <c r="G33" s="161" t="n"/>
+      <c r="H33" s="167" t="n"/>
+      <c r="I33" s="167" t="n"/>
+    </row>
+    <row r="34" ht="19.95" customHeight="1" s="67">
+      <c r="A34" s="108" t="inlineStr">
         <is>
           <t>Registros vigentes</t>
-        </is>
-      </c>
-      <c r="B32" s="31" t="n"/>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="32" t="n"/>
-      <c r="G32" s="119">
-        <f>COUNTIF(I15:I31,"Vigente")</f>
-        <v/>
-      </c>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="32" t="n"/>
-    </row>
-    <row r="33" ht="19.95" customHeight="1" s="67">
-      <c r="A33" s="87" t="inlineStr">
-        <is>
-          <t>Los tiempos de conservación y los lugares de archivo escritos son una propuesta: se ajustan a lo que exija el contrato, la interventoría y la política de la empresa.</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="n"/>
-      <c r="C33" s="31" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="31" t="n"/>
-      <c r="G33" s="31" t="n"/>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="32" t="n"/>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" s="67">
-      <c r="A34" s="77" t="inlineStr">
-        <is>
-          <t>3. FIRMAS</t>
         </is>
       </c>
       <c r="B34" s="31" t="n"/>
       <c r="C34" s="31" t="n"/>
       <c r="D34" s="31" t="n"/>
       <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
+      <c r="F34" s="32" t="n"/>
+      <c r="G34" s="119">
+        <f>COUNTIF(I15:I33,"Vigente")</f>
+        <v/>
+      </c>
       <c r="H34" s="31" t="n"/>
       <c r="I34" s="32" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1" s="67">
-      <c r="A35" s="88" t="inlineStr">
-        <is>
-          <t>ELABORÓ — INSPECTOR / INGENIERO DE CALIDAD</t>
+    <row r="35" ht="19.95" customHeight="1" s="67">
+      <c r="A35" s="87" t="inlineStr">
+        <is>
+          <t>Los tiempos de conservación y los lugares de archivo escritos son una propuesta: se ajustan a lo que exija el contrato, la interventoría y la política de la empresa.</t>
         </is>
       </c>
       <c r="B35" s="31" t="n"/>
-      <c r="C35" s="32" t="n"/>
-      <c r="D35" s="88" t="inlineStr">
-        <is>
-          <t>REVISÓ — RESIDENTE DE OBRA</t>
-        </is>
-      </c>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="31" t="n"/>
       <c r="E35" s="31" t="n"/>
-      <c r="F35" s="32" t="n"/>
-      <c r="G35" s="88" t="inlineStr">
-        <is>
-          <t>Vo.Bo. — GERENCIA / INTERVENTORÍA</t>
-        </is>
-      </c>
+      <c r="F35" s="31" t="n"/>
+      <c r="G35" s="31" t="n"/>
       <c r="H35" s="31" t="n"/>
       <c r="I35" s="32" t="n"/>
     </row>
-    <row r="36" ht="42" customHeight="1" s="67">
-      <c r="A36" s="89" t="inlineStr">
+    <row r="36" ht="16.5" customHeight="1" s="67">
+      <c r="A36" s="77" t="inlineStr">
+        <is>
+          <t>3. FIRMAS</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="n"/>
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="32" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="67">
+      <c r="A37" s="88" t="inlineStr">
+        <is>
+          <t>ELABORÓ — INSPECTOR / INGENIERO DE CALIDAD</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="n"/>
+      <c r="C37" s="32" t="n"/>
+      <c r="D37" s="88" t="inlineStr">
+        <is>
+          <t>REVISÓ — RESIDENTE DE OBRA</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="32" t="n"/>
+      <c r="G37" s="88" t="inlineStr">
+        <is>
+          <t>Vo.Bo. — GERENCIA / INTERVENTORÍA</t>
+        </is>
+      </c>
+      <c r="H37" s="31" t="n"/>
+      <c r="I37" s="32" t="n"/>
+    </row>
+    <row r="38" ht="42" customHeight="1" s="67">
+      <c r="A38" s="89" t="inlineStr">
         <is>
           <t>Firma:</t>
-        </is>
-      </c>
-      <c r="B36" s="32" t="n"/>
-      <c r="C36" s="161" t="n"/>
-      <c r="D36" s="89" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="E36" s="32" t="n"/>
-      <c r="F36" s="161" t="n"/>
-      <c r="G36" s="89" t="inlineStr">
-        <is>
-          <t>Firma:</t>
-        </is>
-      </c>
-      <c r="H36" s="32" t="n"/>
-      <c r="I36" s="161" t="n"/>
-    </row>
-    <row r="37" ht="21" customHeight="1" s="67">
-      <c r="A37" s="89" t="inlineStr">
-        <is>
-          <t>Nombre:</t>
-        </is>
-      </c>
-      <c r="B37" s="32" t="n"/>
-      <c r="C37" s="161" t="n"/>
-      <c r="D37" s="89" t="inlineStr">
-        <is>
-          <t>Nombre:</t>
-        </is>
-      </c>
-      <c r="E37" s="32" t="n"/>
-      <c r="F37" s="161" t="n"/>
-      <c r="G37" s="89" t="inlineStr">
-        <is>
-          <t>Nombre:</t>
-        </is>
-      </c>
-      <c r="H37" s="32" t="n"/>
-      <c r="I37" s="161" t="n"/>
-    </row>
-    <row r="38" ht="21" customHeight="1" s="67">
-      <c r="A38" s="89" t="inlineStr">
-        <is>
-          <t>Cargo:</t>
         </is>
       </c>
       <c r="B38" s="32" t="n"/>
       <c r="C38" s="161" t="n"/>
       <c r="D38" s="89" t="inlineStr">
         <is>
-          <t>Cargo:</t>
+          <t>Firma:</t>
         </is>
       </c>
       <c r="E38" s="32" t="n"/>
       <c r="F38" s="161" t="n"/>
       <c r="G38" s="89" t="inlineStr">
         <is>
-          <t>Cargo:</t>
+          <t>Firma:</t>
         </is>
       </c>
       <c r="H38" s="32" t="n"/>
       <c r="I38" s="161" t="n"/>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="39" ht="21" customHeight="1" s="67">
+      <c r="A39" s="89" t="inlineStr">
+        <is>
+          <t>Nombre:</t>
+        </is>
+      </c>
+      <c r="B39" s="32" t="n"/>
+      <c r="C39" s="161" t="n"/>
+      <c r="D39" s="89" t="inlineStr">
+        <is>
+          <t>Nombre:</t>
+        </is>
+      </c>
+      <c r="E39" s="32" t="n"/>
+      <c r="F39" s="161" t="n"/>
+      <c r="G39" s="89" t="inlineStr">
+        <is>
+          <t>Nombre:</t>
+        </is>
+      </c>
+      <c r="H39" s="32" t="n"/>
+      <c r="I39" s="161" t="n"/>
+    </row>
+    <row r="40" ht="21" customHeight="1" s="67">
+      <c r="A40" s="89" t="inlineStr">
+        <is>
+          <t>Cargo:</t>
+        </is>
+      </c>
+      <c r="B40" s="32" t="n"/>
+      <c r="C40" s="161" t="n"/>
+      <c r="D40" s="89" t="inlineStr">
+        <is>
+          <t>Cargo:</t>
+        </is>
+      </c>
+      <c r="E40" s="32" t="n"/>
+      <c r="F40" s="161" t="n"/>
+      <c r="G40" s="89" t="inlineStr">
+        <is>
+          <t>Cargo:</t>
+        </is>
+      </c>
+      <c r="H40" s="32" t="n"/>
+      <c r="I40" s="161" t="n"/>
+    </row>
+    <row r="41" s="67">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>REV. 09/10/2026</t>
         </is>
       </c>
-      <c r="E39" s="33">
+      <c r="E41" s="33">
         <f>H5</f>
         <v/>
       </c>
@@ -12849,41 +12936,41 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="35">
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="G37:I37"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="E39:I39"/>
-    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="G39:H39"/>
     <mergeCell ref="D1:I2"/>
-    <mergeCell ref="A33:I33"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="G38:H38"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="D3:I3"/>
-    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="G32:I32"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="A13:I13"/>
-    <mergeCell ref="D37:E37"/>
     <mergeCell ref="F12:I12"/>
-    <mergeCell ref="D35:F35"/>
     <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="D39:E39"/>
     <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="E41:I41"/>
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="H8:I8"/>
+    <mergeCell ref="G40:H40"/>
     <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.7" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/public/plantilla-cal-maestro.xlsx
+++ b/public/plantilla-cal-maestro.xlsx
@@ -11402,32 +11402,32 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>2</col>
-      <colOff>2252203</colOff>
-      <row>7</row>
-      <rowOff>177646</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2252203</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>177646</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </blipFill>
-      <spPr>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="0"/>
           <a:ext cx="3564000" cy="1692000"/>
@@ -11438,11 +11438,11 @@
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/plantilla-cal-maestro.xlsx
+++ b/public/plantilla-cal-maestro.xlsx
@@ -15,11 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="#,##0.##"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="hh:mm"/>
+  <numFmts count="2">
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -637,7 +635,7 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -725,34 +723,34 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -926,7 +924,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="19" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -938,7 +936,7 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -947,7 +945,7 @@
     <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -968,28 +966,28 @@
     <xf numFmtId="9" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -1063,7 +1061,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1102,11 +1100,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -11744,10 +11742,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="4" tint="0.3999755851924192"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I142"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="67" min="1" max="1"/>
@@ -11764,7 +11761,7 @@
     <row r="1" ht="40.05" customHeight="1" s="67">
       <c r="D1" s="63" t="inlineStr">
         <is>
-          <t>LISTADO MAESTRO DE REGISTROS DE CALIDAD</t>
+          <t>LISTADO MAESTRO DE REGISTROS</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11861,7 @@
     <row r="9" ht="15" customHeight="1" s="67">
       <c r="A9" s="75" t="inlineStr">
         <is>
-          <t>Qué registros existen, quién los llena, con qué frecuencia y cuánto se conservan</t>
+          <t>Qué registros existen en la empresa (Calidad, SG-SST, Ambiental, Presupuesto y Técnica), quién los llena, con qué frecuencia y cuánto se conservan</t>
         </is>
       </c>
       <c r="B9" s="31" t="n"/>
@@ -11936,7 +11933,7 @@
     <row r="13" ht="16.5" customHeight="1" s="67">
       <c r="A13" s="77" t="inlineStr">
         <is>
-          <t>2. REGISTROS DE CALIDAD</t>
+          <t>2. REGISTROS</t>
         </is>
       </c>
       <c r="B13" s="31" t="n"/>
@@ -12769,166 +12766,1479 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="22.05" customHeight="1" s="67">
+    <row r="33" ht="29" customHeight="1" s="67">
       <c r="A33" s="116" t="n">
         <v>19</v>
       </c>
-      <c r="B33" s="161" t="n"/>
-      <c r="C33" s="161" t="n"/>
-      <c r="D33" s="161" t="n"/>
-      <c r="E33" s="161" t="n"/>
-      <c r="F33" s="161" t="n"/>
-      <c r="G33" s="161" t="n"/>
-      <c r="H33" s="167" t="n"/>
-      <c r="I33" s="167" t="n"/>
+      <c r="B33" s="166" t="n"/>
+      <c r="C33" s="166" t="n"/>
+      <c r="D33" s="166" t="n"/>
+      <c r="E33" s="166" t="n"/>
+      <c r="F33" s="166" t="n"/>
+      <c r="G33" s="166" t="n"/>
+      <c r="H33" s="116" t="n"/>
+      <c r="I33" s="116" t="n"/>
     </row>
-    <row r="34" ht="19.95" customHeight="1" s="67">
-      <c r="A34" s="108" t="inlineStr">
+    <row r="34" ht="29" customHeight="1" s="67">
+      <c r="A34" s="116" t="n">
+        <v>20</v>
+      </c>
+      <c r="B34" s="166" t="n"/>
+      <c r="C34" s="166" t="n"/>
+      <c r="D34" s="166" t="n"/>
+      <c r="E34" s="166" t="n"/>
+      <c r="F34" s="166" t="n"/>
+      <c r="G34" s="166" t="n"/>
+      <c r="H34" s="116" t="n"/>
+      <c r="I34" s="116" t="n"/>
+    </row>
+    <row r="35" ht="29" customHeight="1" s="67">
+      <c r="A35" s="116" t="n">
+        <v>21</v>
+      </c>
+      <c r="B35" s="166" t="n"/>
+      <c r="C35" s="166" t="n"/>
+      <c r="D35" s="166" t="n"/>
+      <c r="E35" s="166" t="n"/>
+      <c r="F35" s="166" t="n"/>
+      <c r="G35" s="166" t="n"/>
+      <c r="H35" s="116" t="n"/>
+      <c r="I35" s="116" t="n"/>
+    </row>
+    <row r="36" ht="29" customHeight="1" s="67">
+      <c r="A36" s="116" t="n">
+        <v>22</v>
+      </c>
+      <c r="B36" s="166" t="n"/>
+      <c r="C36" s="166" t="n"/>
+      <c r="D36" s="166" t="n"/>
+      <c r="E36" s="166" t="n"/>
+      <c r="F36" s="166" t="n"/>
+      <c r="G36" s="166" t="n"/>
+      <c r="H36" s="116" t="n"/>
+      <c r="I36" s="116" t="n"/>
+    </row>
+    <row r="37" ht="29" customHeight="1" s="67">
+      <c r="A37" s="116" t="n">
+        <v>23</v>
+      </c>
+      <c r="B37" s="166" t="n"/>
+      <c r="C37" s="166" t="n"/>
+      <c r="D37" s="166" t="n"/>
+      <c r="E37" s="166" t="n"/>
+      <c r="F37" s="166" t="n"/>
+      <c r="G37" s="166" t="n"/>
+      <c r="H37" s="116" t="n"/>
+      <c r="I37" s="116" t="n"/>
+    </row>
+    <row r="38" ht="29" customHeight="1" s="67">
+      <c r="A38" s="116" t="n">
+        <v>24</v>
+      </c>
+      <c r="B38" s="166" t="n"/>
+      <c r="C38" s="166" t="n"/>
+      <c r="D38" s="166" t="n"/>
+      <c r="E38" s="166" t="n"/>
+      <c r="F38" s="166" t="n"/>
+      <c r="G38" s="166" t="n"/>
+      <c r="H38" s="116" t="n"/>
+      <c r="I38" s="116" t="n"/>
+    </row>
+    <row r="39" ht="29" customHeight="1" s="67">
+      <c r="A39" s="116" t="n">
+        <v>25</v>
+      </c>
+      <c r="B39" s="166" t="n"/>
+      <c r="C39" s="166" t="n"/>
+      <c r="D39" s="166" t="n"/>
+      <c r="E39" s="166" t="n"/>
+      <c r="F39" s="166" t="n"/>
+      <c r="G39" s="166" t="n"/>
+      <c r="H39" s="116" t="n"/>
+      <c r="I39" s="116" t="n"/>
+    </row>
+    <row r="40" ht="29" customHeight="1" s="67">
+      <c r="A40" s="116" t="n">
+        <v>26</v>
+      </c>
+      <c r="B40" s="166" t="n"/>
+      <c r="C40" s="166" t="n"/>
+      <c r="D40" s="166" t="n"/>
+      <c r="E40" s="166" t="n"/>
+      <c r="F40" s="166" t="n"/>
+      <c r="G40" s="166" t="n"/>
+      <c r="H40" s="116" t="n"/>
+      <c r="I40" s="116" t="n"/>
+    </row>
+    <row r="41" ht="29" customHeight="1" s="67">
+      <c r="A41" s="116" t="n">
+        <v>27</v>
+      </c>
+      <c r="B41" s="166" t="n"/>
+      <c r="C41" s="166" t="n"/>
+      <c r="D41" s="166" t="n"/>
+      <c r="E41" s="166" t="n"/>
+      <c r="F41" s="166" t="n"/>
+      <c r="G41" s="166" t="n"/>
+      <c r="H41" s="116" t="n"/>
+      <c r="I41" s="116" t="n"/>
+    </row>
+    <row r="42" ht="29" customHeight="1" s="67">
+      <c r="A42" s="116" t="n">
+        <v>28</v>
+      </c>
+      <c r="B42" s="166" t="n"/>
+      <c r="C42" s="166" t="n"/>
+      <c r="D42" s="166" t="n"/>
+      <c r="E42" s="166" t="n"/>
+      <c r="F42" s="166" t="n"/>
+      <c r="G42" s="166" t="n"/>
+      <c r="H42" s="116" t="n"/>
+      <c r="I42" s="116" t="n"/>
+    </row>
+    <row r="43" ht="29" customHeight="1" s="67">
+      <c r="A43" s="116" t="n">
+        <v>29</v>
+      </c>
+      <c r="B43" s="166" t="n"/>
+      <c r="C43" s="166" t="n"/>
+      <c r="D43" s="166" t="n"/>
+      <c r="E43" s="166" t="n"/>
+      <c r="F43" s="166" t="n"/>
+      <c r="G43" s="166" t="n"/>
+      <c r="H43" s="116" t="n"/>
+      <c r="I43" s="116" t="n"/>
+    </row>
+    <row r="44" ht="29" customHeight="1" s="67">
+      <c r="A44" s="116" t="n">
+        <v>30</v>
+      </c>
+      <c r="B44" s="166" t="n"/>
+      <c r="C44" s="166" t="n"/>
+      <c r="D44" s="166" t="n"/>
+      <c r="E44" s="166" t="n"/>
+      <c r="F44" s="166" t="n"/>
+      <c r="G44" s="166" t="n"/>
+      <c r="H44" s="116" t="n"/>
+      <c r="I44" s="116" t="n"/>
+    </row>
+    <row r="45" ht="29" customHeight="1" s="67">
+      <c r="A45" s="116" t="n">
+        <v>31</v>
+      </c>
+      <c r="B45" s="166" t="n"/>
+      <c r="C45" s="166" t="n"/>
+      <c r="D45" s="166" t="n"/>
+      <c r="E45" s="166" t="n"/>
+      <c r="F45" s="166" t="n"/>
+      <c r="G45" s="166" t="n"/>
+      <c r="H45" s="116" t="n"/>
+      <c r="I45" s="116" t="n"/>
+    </row>
+    <row r="46" ht="29" customHeight="1" s="67">
+      <c r="A46" s="116" t="n">
+        <v>32</v>
+      </c>
+      <c r="B46" s="166" t="n"/>
+      <c r="C46" s="166" t="n"/>
+      <c r="D46" s="166" t="n"/>
+      <c r="E46" s="166" t="n"/>
+      <c r="F46" s="166" t="n"/>
+      <c r="G46" s="166" t="n"/>
+      <c r="H46" s="116" t="n"/>
+      <c r="I46" s="116" t="n"/>
+    </row>
+    <row r="47" ht="29" customHeight="1" s="67">
+      <c r="A47" s="116" t="n">
+        <v>33</v>
+      </c>
+      <c r="B47" s="166" t="n"/>
+      <c r="C47" s="166" t="n"/>
+      <c r="D47" s="166" t="n"/>
+      <c r="E47" s="166" t="n"/>
+      <c r="F47" s="166" t="n"/>
+      <c r="G47" s="166" t="n"/>
+      <c r="H47" s="116" t="n"/>
+      <c r="I47" s="116" t="n"/>
+    </row>
+    <row r="48" ht="29" customHeight="1" s="67">
+      <c r="A48" s="116" t="n">
+        <v>34</v>
+      </c>
+      <c r="B48" s="166" t="n"/>
+      <c r="C48" s="166" t="n"/>
+      <c r="D48" s="166" t="n"/>
+      <c r="E48" s="166" t="n"/>
+      <c r="F48" s="166" t="n"/>
+      <c r="G48" s="166" t="n"/>
+      <c r="H48" s="116" t="n"/>
+      <c r="I48" s="116" t="n"/>
+    </row>
+    <row r="49" ht="29" customHeight="1" s="67">
+      <c r="A49" s="116" t="n">
+        <v>35</v>
+      </c>
+      <c r="B49" s="166" t="n"/>
+      <c r="C49" s="166" t="n"/>
+      <c r="D49" s="166" t="n"/>
+      <c r="E49" s="166" t="n"/>
+      <c r="F49" s="166" t="n"/>
+      <c r="G49" s="166" t="n"/>
+      <c r="H49" s="116" t="n"/>
+      <c r="I49" s="116" t="n"/>
+    </row>
+    <row r="50" ht="29" customHeight="1" s="67">
+      <c r="A50" s="116" t="n">
+        <v>36</v>
+      </c>
+      <c r="B50" s="166" t="n"/>
+      <c r="C50" s="166" t="n"/>
+      <c r="D50" s="166" t="n"/>
+      <c r="E50" s="166" t="n"/>
+      <c r="F50" s="166" t="n"/>
+      <c r="G50" s="166" t="n"/>
+      <c r="H50" s="116" t="n"/>
+      <c r="I50" s="116" t="n"/>
+    </row>
+    <row r="51" ht="29" customHeight="1" s="67">
+      <c r="A51" s="116" t="n">
+        <v>37</v>
+      </c>
+      <c r="B51" s="166" t="n"/>
+      <c r="C51" s="166" t="n"/>
+      <c r="D51" s="166" t="n"/>
+      <c r="E51" s="166" t="n"/>
+      <c r="F51" s="166" t="n"/>
+      <c r="G51" s="166" t="n"/>
+      <c r="H51" s="116" t="n"/>
+      <c r="I51" s="116" t="n"/>
+    </row>
+    <row r="52" ht="29" customHeight="1" s="67">
+      <c r="A52" s="116" t="n">
+        <v>38</v>
+      </c>
+      <c r="B52" s="166" t="n"/>
+      <c r="C52" s="166" t="n"/>
+      <c r="D52" s="166" t="n"/>
+      <c r="E52" s="166" t="n"/>
+      <c r="F52" s="166" t="n"/>
+      <c r="G52" s="166" t="n"/>
+      <c r="H52" s="116" t="n"/>
+      <c r="I52" s="116" t="n"/>
+    </row>
+    <row r="53" ht="29" customHeight="1" s="67">
+      <c r="A53" s="116" t="n">
+        <v>39</v>
+      </c>
+      <c r="B53" s="166" t="n"/>
+      <c r="C53" s="166" t="n"/>
+      <c r="D53" s="166" t="n"/>
+      <c r="E53" s="166" t="n"/>
+      <c r="F53" s="166" t="n"/>
+      <c r="G53" s="166" t="n"/>
+      <c r="H53" s="116" t="n"/>
+      <c r="I53" s="116" t="n"/>
+    </row>
+    <row r="54" ht="29" customHeight="1" s="67">
+      <c r="A54" s="116" t="n">
+        <v>40</v>
+      </c>
+      <c r="B54" s="166" t="n"/>
+      <c r="C54" s="166" t="n"/>
+      <c r="D54" s="166" t="n"/>
+      <c r="E54" s="166" t="n"/>
+      <c r="F54" s="166" t="n"/>
+      <c r="G54" s="166" t="n"/>
+      <c r="H54" s="116" t="n"/>
+      <c r="I54" s="116" t="n"/>
+    </row>
+    <row r="55" ht="29" customHeight="1" s="67">
+      <c r="A55" s="116" t="n">
+        <v>41</v>
+      </c>
+      <c r="B55" s="166" t="n"/>
+      <c r="C55" s="166" t="n"/>
+      <c r="D55" s="166" t="n"/>
+      <c r="E55" s="166" t="n"/>
+      <c r="F55" s="166" t="n"/>
+      <c r="G55" s="166" t="n"/>
+      <c r="H55" s="116" t="n"/>
+      <c r="I55" s="116" t="n"/>
+    </row>
+    <row r="56" ht="29" customHeight="1" s="67">
+      <c r="A56" s="116" t="n">
+        <v>42</v>
+      </c>
+      <c r="B56" s="166" t="n"/>
+      <c r="C56" s="166" t="n"/>
+      <c r="D56" s="166" t="n"/>
+      <c r="E56" s="166" t="n"/>
+      <c r="F56" s="166" t="n"/>
+      <c r="G56" s="166" t="n"/>
+      <c r="H56" s="116" t="n"/>
+      <c r="I56" s="116" t="n"/>
+    </row>
+    <row r="57" ht="29" customHeight="1" s="67">
+      <c r="A57" s="116" t="n">
+        <v>43</v>
+      </c>
+      <c r="B57" s="166" t="n"/>
+      <c r="C57" s="166" t="n"/>
+      <c r="D57" s="166" t="n"/>
+      <c r="E57" s="166" t="n"/>
+      <c r="F57" s="166" t="n"/>
+      <c r="G57" s="166" t="n"/>
+      <c r="H57" s="116" t="n"/>
+      <c r="I57" s="116" t="n"/>
+    </row>
+    <row r="58" ht="29" customHeight="1" s="67">
+      <c r="A58" s="116" t="n">
+        <v>44</v>
+      </c>
+      <c r="B58" s="166" t="n"/>
+      <c r="C58" s="166" t="n"/>
+      <c r="D58" s="166" t="n"/>
+      <c r="E58" s="166" t="n"/>
+      <c r="F58" s="166" t="n"/>
+      <c r="G58" s="166" t="n"/>
+      <c r="H58" s="116" t="n"/>
+      <c r="I58" s="116" t="n"/>
+    </row>
+    <row r="59" ht="29" customHeight="1" s="67">
+      <c r="A59" s="116" t="n">
+        <v>45</v>
+      </c>
+      <c r="B59" s="166" t="n"/>
+      <c r="C59" s="166" t="n"/>
+      <c r="D59" s="166" t="n"/>
+      <c r="E59" s="166" t="n"/>
+      <c r="F59" s="166" t="n"/>
+      <c r="G59" s="166" t="n"/>
+      <c r="H59" s="116" t="n"/>
+      <c r="I59" s="116" t="n"/>
+    </row>
+    <row r="60" ht="29" customHeight="1" s="67">
+      <c r="A60" s="116" t="n">
+        <v>46</v>
+      </c>
+      <c r="B60" s="166" t="n"/>
+      <c r="C60" s="166" t="n"/>
+      <c r="D60" s="166" t="n"/>
+      <c r="E60" s="166" t="n"/>
+      <c r="F60" s="166" t="n"/>
+      <c r="G60" s="166" t="n"/>
+      <c r="H60" s="116" t="n"/>
+      <c r="I60" s="116" t="n"/>
+    </row>
+    <row r="61" ht="29" customHeight="1" s="67">
+      <c r="A61" s="116" t="n">
+        <v>47</v>
+      </c>
+      <c r="B61" s="166" t="n"/>
+      <c r="C61" s="166" t="n"/>
+      <c r="D61" s="166" t="n"/>
+      <c r="E61" s="166" t="n"/>
+      <c r="F61" s="166" t="n"/>
+      <c r="G61" s="166" t="n"/>
+      <c r="H61" s="116" t="n"/>
+      <c r="I61" s="116" t="n"/>
+    </row>
+    <row r="62" ht="29" customHeight="1" s="67">
+      <c r="A62" s="116" t="n">
+        <v>48</v>
+      </c>
+      <c r="B62" s="166" t="n"/>
+      <c r="C62" s="166" t="n"/>
+      <c r="D62" s="166" t="n"/>
+      <c r="E62" s="166" t="n"/>
+      <c r="F62" s="166" t="n"/>
+      <c r="G62" s="166" t="n"/>
+      <c r="H62" s="116" t="n"/>
+      <c r="I62" s="116" t="n"/>
+    </row>
+    <row r="63" ht="29" customHeight="1" s="67">
+      <c r="A63" s="116" t="n">
+        <v>49</v>
+      </c>
+      <c r="B63" s="166" t="n"/>
+      <c r="C63" s="166" t="n"/>
+      <c r="D63" s="166" t="n"/>
+      <c r="E63" s="166" t="n"/>
+      <c r="F63" s="166" t="n"/>
+      <c r="G63" s="166" t="n"/>
+      <c r="H63" s="116" t="n"/>
+      <c r="I63" s="116" t="n"/>
+    </row>
+    <row r="64" ht="29" customHeight="1" s="67">
+      <c r="A64" s="116" t="n">
+        <v>50</v>
+      </c>
+      <c r="B64" s="166" t="n"/>
+      <c r="C64" s="166" t="n"/>
+      <c r="D64" s="166" t="n"/>
+      <c r="E64" s="166" t="n"/>
+      <c r="F64" s="166" t="n"/>
+      <c r="G64" s="166" t="n"/>
+      <c r="H64" s="116" t="n"/>
+      <c r="I64" s="116" t="n"/>
+    </row>
+    <row r="65" ht="29" customHeight="1" s="67">
+      <c r="A65" s="116" t="n">
+        <v>51</v>
+      </c>
+      <c r="B65" s="166" t="n"/>
+      <c r="C65" s="166" t="n"/>
+      <c r="D65" s="166" t="n"/>
+      <c r="E65" s="166" t="n"/>
+      <c r="F65" s="166" t="n"/>
+      <c r="G65" s="166" t="n"/>
+      <c r="H65" s="116" t="n"/>
+      <c r="I65" s="116" t="n"/>
+    </row>
+    <row r="66" ht="29" customHeight="1" s="67">
+      <c r="A66" s="116" t="n">
+        <v>52</v>
+      </c>
+      <c r="B66" s="166" t="n"/>
+      <c r="C66" s="166" t="n"/>
+      <c r="D66" s="166" t="n"/>
+      <c r="E66" s="166" t="n"/>
+      <c r="F66" s="166" t="n"/>
+      <c r="G66" s="166" t="n"/>
+      <c r="H66" s="116" t="n"/>
+      <c r="I66" s="116" t="n"/>
+    </row>
+    <row r="67" ht="29" customHeight="1" s="67">
+      <c r="A67" s="116" t="n">
+        <v>53</v>
+      </c>
+      <c r="B67" s="166" t="n"/>
+      <c r="C67" s="166" t="n"/>
+      <c r="D67" s="166" t="n"/>
+      <c r="E67" s="166" t="n"/>
+      <c r="F67" s="166" t="n"/>
+      <c r="G67" s="166" t="n"/>
+      <c r="H67" s="116" t="n"/>
+      <c r="I67" s="116" t="n"/>
+    </row>
+    <row r="68" ht="29" customHeight="1" s="67">
+      <c r="A68" s="116" t="n">
+        <v>54</v>
+      </c>
+      <c r="B68" s="166" t="n"/>
+      <c r="C68" s="166" t="n"/>
+      <c r="D68" s="166" t="n"/>
+      <c r="E68" s="166" t="n"/>
+      <c r="F68" s="166" t="n"/>
+      <c r="G68" s="166" t="n"/>
+      <c r="H68" s="116" t="n"/>
+      <c r="I68" s="116" t="n"/>
+    </row>
+    <row r="69" ht="29" customHeight="1" s="67">
+      <c r="A69" s="116" t="n">
+        <v>55</v>
+      </c>
+      <c r="B69" s="166" t="n"/>
+      <c r="C69" s="166" t="n"/>
+      <c r="D69" s="166" t="n"/>
+      <c r="E69" s="166" t="n"/>
+      <c r="F69" s="166" t="n"/>
+      <c r="G69" s="166" t="n"/>
+      <c r="H69" s="116" t="n"/>
+      <c r="I69" s="116" t="n"/>
+    </row>
+    <row r="70" ht="29" customHeight="1" s="67">
+      <c r="A70" s="116" t="n">
+        <v>56</v>
+      </c>
+      <c r="B70" s="166" t="n"/>
+      <c r="C70" s="166" t="n"/>
+      <c r="D70" s="166" t="n"/>
+      <c r="E70" s="166" t="n"/>
+      <c r="F70" s="166" t="n"/>
+      <c r="G70" s="166" t="n"/>
+      <c r="H70" s="116" t="n"/>
+      <c r="I70" s="116" t="n"/>
+    </row>
+    <row r="71" ht="29" customHeight="1" s="67">
+      <c r="A71" s="116" t="n">
+        <v>57</v>
+      </c>
+      <c r="B71" s="166" t="n"/>
+      <c r="C71" s="166" t="n"/>
+      <c r="D71" s="166" t="n"/>
+      <c r="E71" s="166" t="n"/>
+      <c r="F71" s="166" t="n"/>
+      <c r="G71" s="166" t="n"/>
+      <c r="H71" s="116" t="n"/>
+      <c r="I71" s="116" t="n"/>
+    </row>
+    <row r="72" ht="29" customHeight="1" s="67">
+      <c r="A72" s="116" t="n">
+        <v>58</v>
+      </c>
+      <c r="B72" s="166" t="n"/>
+      <c r="C72" s="166" t="n"/>
+      <c r="D72" s="166" t="n"/>
+      <c r="E72" s="166" t="n"/>
+      <c r="F72" s="166" t="n"/>
+      <c r="G72" s="166" t="n"/>
+      <c r="H72" s="116" t="n"/>
+      <c r="I72" s="116" t="n"/>
+    </row>
+    <row r="73" ht="29" customHeight="1" s="67">
+      <c r="A73" s="116" t="n">
+        <v>59</v>
+      </c>
+      <c r="B73" s="166" t="n"/>
+      <c r="C73" s="166" t="n"/>
+      <c r="D73" s="166" t="n"/>
+      <c r="E73" s="166" t="n"/>
+      <c r="F73" s="166" t="n"/>
+      <c r="G73" s="166" t="n"/>
+      <c r="H73" s="116" t="n"/>
+      <c r="I73" s="116" t="n"/>
+    </row>
+    <row r="74" ht="29" customHeight="1" s="67">
+      <c r="A74" s="116" t="n">
+        <v>60</v>
+      </c>
+      <c r="B74" s="166" t="n"/>
+      <c r="C74" s="166" t="n"/>
+      <c r="D74" s="166" t="n"/>
+      <c r="E74" s="166" t="n"/>
+      <c r="F74" s="166" t="n"/>
+      <c r="G74" s="166" t="n"/>
+      <c r="H74" s="116" t="n"/>
+      <c r="I74" s="116" t="n"/>
+    </row>
+    <row r="75" ht="29" customHeight="1" s="67">
+      <c r="A75" s="116" t="n">
+        <v>61</v>
+      </c>
+      <c r="B75" s="166" t="n"/>
+      <c r="C75" s="166" t="n"/>
+      <c r="D75" s="166" t="n"/>
+      <c r="E75" s="166" t="n"/>
+      <c r="F75" s="166" t="n"/>
+      <c r="G75" s="166" t="n"/>
+      <c r="H75" s="116" t="n"/>
+      <c r="I75" s="116" t="n"/>
+    </row>
+    <row r="76" ht="29" customHeight="1" s="67">
+      <c r="A76" s="116" t="n">
+        <v>62</v>
+      </c>
+      <c r="B76" s="166" t="n"/>
+      <c r="C76" s="166" t="n"/>
+      <c r="D76" s="166" t="n"/>
+      <c r="E76" s="166" t="n"/>
+      <c r="F76" s="166" t="n"/>
+      <c r="G76" s="166" t="n"/>
+      <c r="H76" s="116" t="n"/>
+      <c r="I76" s="116" t="n"/>
+    </row>
+    <row r="77" ht="29" customHeight="1" s="67">
+      <c r="A77" s="116" t="n">
+        <v>63</v>
+      </c>
+      <c r="B77" s="166" t="n"/>
+      <c r="C77" s="166" t="n"/>
+      <c r="D77" s="166" t="n"/>
+      <c r="E77" s="166" t="n"/>
+      <c r="F77" s="166" t="n"/>
+      <c r="G77" s="166" t="n"/>
+      <c r="H77" s="116" t="n"/>
+      <c r="I77" s="116" t="n"/>
+    </row>
+    <row r="78" ht="29" customHeight="1" s="67">
+      <c r="A78" s="116" t="n">
+        <v>64</v>
+      </c>
+      <c r="B78" s="166" t="n"/>
+      <c r="C78" s="166" t="n"/>
+      <c r="D78" s="166" t="n"/>
+      <c r="E78" s="166" t="n"/>
+      <c r="F78" s="166" t="n"/>
+      <c r="G78" s="166" t="n"/>
+      <c r="H78" s="116" t="n"/>
+      <c r="I78" s="116" t="n"/>
+    </row>
+    <row r="79" ht="29" customHeight="1" s="67">
+      <c r="A79" s="116" t="n">
+        <v>65</v>
+      </c>
+      <c r="B79" s="166" t="n"/>
+      <c r="C79" s="166" t="n"/>
+      <c r="D79" s="166" t="n"/>
+      <c r="E79" s="166" t="n"/>
+      <c r="F79" s="166" t="n"/>
+      <c r="G79" s="166" t="n"/>
+      <c r="H79" s="116" t="n"/>
+      <c r="I79" s="116" t="n"/>
+    </row>
+    <row r="80" ht="29" customHeight="1" s="67">
+      <c r="A80" s="116" t="n">
+        <v>66</v>
+      </c>
+      <c r="B80" s="166" t="n"/>
+      <c r="C80" s="166" t="n"/>
+      <c r="D80" s="166" t="n"/>
+      <c r="E80" s="166" t="n"/>
+      <c r="F80" s="166" t="n"/>
+      <c r="G80" s="166" t="n"/>
+      <c r="H80" s="116" t="n"/>
+      <c r="I80" s="116" t="n"/>
+    </row>
+    <row r="81" ht="29" customHeight="1" s="67">
+      <c r="A81" s="116" t="n">
+        <v>67</v>
+      </c>
+      <c r="B81" s="166" t="n"/>
+      <c r="C81" s="166" t="n"/>
+      <c r="D81" s="166" t="n"/>
+      <c r="E81" s="166" t="n"/>
+      <c r="F81" s="166" t="n"/>
+      <c r="G81" s="166" t="n"/>
+      <c r="H81" s="116" t="n"/>
+      <c r="I81" s="116" t="n"/>
+    </row>
+    <row r="82" ht="29" customHeight="1" s="67">
+      <c r="A82" s="116" t="n">
+        <v>68</v>
+      </c>
+      <c r="B82" s="166" t="n"/>
+      <c r="C82" s="166" t="n"/>
+      <c r="D82" s="166" t="n"/>
+      <c r="E82" s="166" t="n"/>
+      <c r="F82" s="166" t="n"/>
+      <c r="G82" s="166" t="n"/>
+      <c r="H82" s="116" t="n"/>
+      <c r="I82" s="116" t="n"/>
+    </row>
+    <row r="83" ht="29" customHeight="1" s="67">
+      <c r="A83" s="116" t="n">
+        <v>69</v>
+      </c>
+      <c r="B83" s="166" t="n"/>
+      <c r="C83" s="166" t="n"/>
+      <c r="D83" s="166" t="n"/>
+      <c r="E83" s="166" t="n"/>
+      <c r="F83" s="166" t="n"/>
+      <c r="G83" s="166" t="n"/>
+      <c r="H83" s="116" t="n"/>
+      <c r="I83" s="116" t="n"/>
+    </row>
+    <row r="84" ht="29" customHeight="1" s="67">
+      <c r="A84" s="116" t="n">
+        <v>70</v>
+      </c>
+      <c r="B84" s="166" t="n"/>
+      <c r="C84" s="166" t="n"/>
+      <c r="D84" s="166" t="n"/>
+      <c r="E84" s="166" t="n"/>
+      <c r="F84" s="166" t="n"/>
+      <c r="G84" s="166" t="n"/>
+      <c r="H84" s="116" t="n"/>
+      <c r="I84" s="116" t="n"/>
+    </row>
+    <row r="85" ht="29" customHeight="1" s="67">
+      <c r="A85" s="116" t="n">
+        <v>71</v>
+      </c>
+      <c r="B85" s="166" t="n"/>
+      <c r="C85" s="166" t="n"/>
+      <c r="D85" s="166" t="n"/>
+      <c r="E85" s="166" t="n"/>
+      <c r="F85" s="166" t="n"/>
+      <c r="G85" s="166" t="n"/>
+      <c r="H85" s="116" t="n"/>
+      <c r="I85" s="116" t="n"/>
+    </row>
+    <row r="86" ht="29" customHeight="1" s="67">
+      <c r="A86" s="116" t="n">
+        <v>72</v>
+      </c>
+      <c r="B86" s="166" t="n"/>
+      <c r="C86" s="166" t="n"/>
+      <c r="D86" s="166" t="n"/>
+      <c r="E86" s="166" t="n"/>
+      <c r="F86" s="166" t="n"/>
+      <c r="G86" s="166" t="n"/>
+      <c r="H86" s="116" t="n"/>
+      <c r="I86" s="116" t="n"/>
+    </row>
+    <row r="87" ht="29" customHeight="1" s="67">
+      <c r="A87" s="116" t="n">
+        <v>73</v>
+      </c>
+      <c r="B87" s="166" t="n"/>
+      <c r="C87" s="166" t="n"/>
+      <c r="D87" s="166" t="n"/>
+      <c r="E87" s="166" t="n"/>
+      <c r="F87" s="166" t="n"/>
+      <c r="G87" s="166" t="n"/>
+      <c r="H87" s="116" t="n"/>
+      <c r="I87" s="116" t="n"/>
+    </row>
+    <row r="88" ht="29" customHeight="1" s="67">
+      <c r="A88" s="116" t="n">
+        <v>74</v>
+      </c>
+      <c r="B88" s="166" t="n"/>
+      <c r="C88" s="166" t="n"/>
+      <c r="D88" s="166" t="n"/>
+      <c r="E88" s="166" t="n"/>
+      <c r="F88" s="166" t="n"/>
+      <c r="G88" s="166" t="n"/>
+      <c r="H88" s="116" t="n"/>
+      <c r="I88" s="116" t="n"/>
+    </row>
+    <row r="89" ht="29" customHeight="1" s="67">
+      <c r="A89" s="116" t="n">
+        <v>75</v>
+      </c>
+      <c r="B89" s="166" t="n"/>
+      <c r="C89" s="166" t="n"/>
+      <c r="D89" s="166" t="n"/>
+      <c r="E89" s="166" t="n"/>
+      <c r="F89" s="166" t="n"/>
+      <c r="G89" s="166" t="n"/>
+      <c r="H89" s="116" t="n"/>
+      <c r="I89" s="116" t="n"/>
+    </row>
+    <row r="90" ht="29" customHeight="1" s="67">
+      <c r="A90" s="116" t="n">
+        <v>76</v>
+      </c>
+      <c r="B90" s="166" t="n"/>
+      <c r="C90" s="166" t="n"/>
+      <c r="D90" s="166" t="n"/>
+      <c r="E90" s="166" t="n"/>
+      <c r="F90" s="166" t="n"/>
+      <c r="G90" s="166" t="n"/>
+      <c r="H90" s="116" t="n"/>
+      <c r="I90" s="116" t="n"/>
+    </row>
+    <row r="91" ht="29" customHeight="1" s="67">
+      <c r="A91" s="116" t="n">
+        <v>77</v>
+      </c>
+      <c r="B91" s="166" t="n"/>
+      <c r="C91" s="166" t="n"/>
+      <c r="D91" s="166" t="n"/>
+      <c r="E91" s="166" t="n"/>
+      <c r="F91" s="166" t="n"/>
+      <c r="G91" s="166" t="n"/>
+      <c r="H91" s="116" t="n"/>
+      <c r="I91" s="116" t="n"/>
+    </row>
+    <row r="92" ht="29" customHeight="1" s="67">
+      <c r="A92" s="116" t="n">
+        <v>78</v>
+      </c>
+      <c r="B92" s="166" t="n"/>
+      <c r="C92" s="166" t="n"/>
+      <c r="D92" s="166" t="n"/>
+      <c r="E92" s="166" t="n"/>
+      <c r="F92" s="166" t="n"/>
+      <c r="G92" s="166" t="n"/>
+      <c r="H92" s="116" t="n"/>
+      <c r="I92" s="116" t="n"/>
+    </row>
+    <row r="93" ht="29" customHeight="1" s="67">
+      <c r="A93" s="116" t="n">
+        <v>79</v>
+      </c>
+      <c r="B93" s="166" t="n"/>
+      <c r="C93" s="166" t="n"/>
+      <c r="D93" s="166" t="n"/>
+      <c r="E93" s="166" t="n"/>
+      <c r="F93" s="166" t="n"/>
+      <c r="G93" s="166" t="n"/>
+      <c r="H93" s="116" t="n"/>
+      <c r="I93" s="116" t="n"/>
+    </row>
+    <row r="94" ht="29" customHeight="1" s="67">
+      <c r="A94" s="116" t="n">
+        <v>80</v>
+      </c>
+      <c r="B94" s="166" t="n"/>
+      <c r="C94" s="166" t="n"/>
+      <c r="D94" s="166" t="n"/>
+      <c r="E94" s="166" t="n"/>
+      <c r="F94" s="166" t="n"/>
+      <c r="G94" s="166" t="n"/>
+      <c r="H94" s="116" t="n"/>
+      <c r="I94" s="116" t="n"/>
+    </row>
+    <row r="95" ht="29" customHeight="1" s="67">
+      <c r="A95" s="116" t="n">
+        <v>81</v>
+      </c>
+      <c r="B95" s="166" t="n"/>
+      <c r="C95" s="166" t="n"/>
+      <c r="D95" s="166" t="n"/>
+      <c r="E95" s="166" t="n"/>
+      <c r="F95" s="166" t="n"/>
+      <c r="G95" s="166" t="n"/>
+      <c r="H95" s="116" t="n"/>
+      <c r="I95" s="116" t="n"/>
+    </row>
+    <row r="96" ht="29" customHeight="1" s="67">
+      <c r="A96" s="116" t="n">
+        <v>82</v>
+      </c>
+      <c r="B96" s="166" t="n"/>
+      <c r="C96" s="166" t="n"/>
+      <c r="D96" s="166" t="n"/>
+      <c r="E96" s="166" t="n"/>
+      <c r="F96" s="166" t="n"/>
+      <c r="G96" s="166" t="n"/>
+      <c r="H96" s="116" t="n"/>
+      <c r="I96" s="116" t="n"/>
+    </row>
+    <row r="97" ht="29" customHeight="1" s="67">
+      <c r="A97" s="116" t="n">
+        <v>83</v>
+      </c>
+      <c r="B97" s="166" t="n"/>
+      <c r="C97" s="166" t="n"/>
+      <c r="D97" s="166" t="n"/>
+      <c r="E97" s="166" t="n"/>
+      <c r="F97" s="166" t="n"/>
+      <c r="G97" s="166" t="n"/>
+      <c r="H97" s="116" t="n"/>
+      <c r="I97" s="116" t="n"/>
+    </row>
+    <row r="98" ht="29" customHeight="1" s="67">
+      <c r="A98" s="116" t="n">
+        <v>84</v>
+      </c>
+      <c r="B98" s="166" t="n"/>
+      <c r="C98" s="166" t="n"/>
+      <c r="D98" s="166" t="n"/>
+      <c r="E98" s="166" t="n"/>
+      <c r="F98" s="166" t="n"/>
+      <c r="G98" s="166" t="n"/>
+      <c r="H98" s="116" t="n"/>
+      <c r="I98" s="116" t="n"/>
+    </row>
+    <row r="99" ht="29" customHeight="1" s="67">
+      <c r="A99" s="116" t="n">
+        <v>85</v>
+      </c>
+      <c r="B99" s="166" t="n"/>
+      <c r="C99" s="166" t="n"/>
+      <c r="D99" s="166" t="n"/>
+      <c r="E99" s="166" t="n"/>
+      <c r="F99" s="166" t="n"/>
+      <c r="G99" s="166" t="n"/>
+      <c r="H99" s="116" t="n"/>
+      <c r="I99" s="116" t="n"/>
+    </row>
+    <row r="100" ht="29" customHeight="1" s="67">
+      <c r="A100" s="116" t="n">
+        <v>86</v>
+      </c>
+      <c r="B100" s="166" t="n"/>
+      <c r="C100" s="166" t="n"/>
+      <c r="D100" s="166" t="n"/>
+      <c r="E100" s="166" t="n"/>
+      <c r="F100" s="166" t="n"/>
+      <c r="G100" s="166" t="n"/>
+      <c r="H100" s="116" t="n"/>
+      <c r="I100" s="116" t="n"/>
+    </row>
+    <row r="101" ht="29" customHeight="1" s="67">
+      <c r="A101" s="116" t="n">
+        <v>87</v>
+      </c>
+      <c r="B101" s="166" t="n"/>
+      <c r="C101" s="166" t="n"/>
+      <c r="D101" s="166" t="n"/>
+      <c r="E101" s="166" t="n"/>
+      <c r="F101" s="166" t="n"/>
+      <c r="G101" s="166" t="n"/>
+      <c r="H101" s="116" t="n"/>
+      <c r="I101" s="116" t="n"/>
+    </row>
+    <row r="102" ht="29" customHeight="1" s="67">
+      <c r="A102" s="116" t="n">
+        <v>88</v>
+      </c>
+      <c r="B102" s="166" t="n"/>
+      <c r="C102" s="166" t="n"/>
+      <c r="D102" s="166" t="n"/>
+      <c r="E102" s="166" t="n"/>
+      <c r="F102" s="166" t="n"/>
+      <c r="G102" s="166" t="n"/>
+      <c r="H102" s="116" t="n"/>
+      <c r="I102" s="116" t="n"/>
+    </row>
+    <row r="103" ht="29" customHeight="1" s="67">
+      <c r="A103" s="116" t="n">
+        <v>89</v>
+      </c>
+      <c r="B103" s="166" t="n"/>
+      <c r="C103" s="166" t="n"/>
+      <c r="D103" s="166" t="n"/>
+      <c r="E103" s="166" t="n"/>
+      <c r="F103" s="166" t="n"/>
+      <c r="G103" s="166" t="n"/>
+      <c r="H103" s="116" t="n"/>
+      <c r="I103" s="116" t="n"/>
+    </row>
+    <row r="104" ht="29" customHeight="1" s="67">
+      <c r="A104" s="116" t="n">
+        <v>90</v>
+      </c>
+      <c r="B104" s="166" t="n"/>
+      <c r="C104" s="166" t="n"/>
+      <c r="D104" s="166" t="n"/>
+      <c r="E104" s="166" t="n"/>
+      <c r="F104" s="166" t="n"/>
+      <c r="G104" s="166" t="n"/>
+      <c r="H104" s="116" t="n"/>
+      <c r="I104" s="116" t="n"/>
+    </row>
+    <row r="105" ht="29" customHeight="1" s="67">
+      <c r="A105" s="116" t="n">
+        <v>91</v>
+      </c>
+      <c r="B105" s="166" t="n"/>
+      <c r="C105" s="166" t="n"/>
+      <c r="D105" s="166" t="n"/>
+      <c r="E105" s="166" t="n"/>
+      <c r="F105" s="166" t="n"/>
+      <c r="G105" s="166" t="n"/>
+      <c r="H105" s="116" t="n"/>
+      <c r="I105" s="116" t="n"/>
+    </row>
+    <row r="106" ht="29" customHeight="1" s="67">
+      <c r="A106" s="116" t="n">
+        <v>92</v>
+      </c>
+      <c r="B106" s="166" t="n"/>
+      <c r="C106" s="166" t="n"/>
+      <c r="D106" s="166" t="n"/>
+      <c r="E106" s="166" t="n"/>
+      <c r="F106" s="166" t="n"/>
+      <c r="G106" s="166" t="n"/>
+      <c r="H106" s="116" t="n"/>
+      <c r="I106" s="116" t="n"/>
+    </row>
+    <row r="107" ht="29" customHeight="1" s="67">
+      <c r="A107" s="116" t="n">
+        <v>93</v>
+      </c>
+      <c r="B107" s="166" t="n"/>
+      <c r="C107" s="166" t="n"/>
+      <c r="D107" s="166" t="n"/>
+      <c r="E107" s="166" t="n"/>
+      <c r="F107" s="166" t="n"/>
+      <c r="G107" s="166" t="n"/>
+      <c r="H107" s="116" t="n"/>
+      <c r="I107" s="116" t="n"/>
+    </row>
+    <row r="108" ht="29" customHeight="1" s="67">
+      <c r="A108" s="116" t="n">
+        <v>94</v>
+      </c>
+      <c r="B108" s="166" t="n"/>
+      <c r="C108" s="166" t="n"/>
+      <c r="D108" s="166" t="n"/>
+      <c r="E108" s="166" t="n"/>
+      <c r="F108" s="166" t="n"/>
+      <c r="G108" s="166" t="n"/>
+      <c r="H108" s="116" t="n"/>
+      <c r="I108" s="116" t="n"/>
+    </row>
+    <row r="109" ht="29" customHeight="1" s="67">
+      <c r="A109" s="116" t="n">
+        <v>95</v>
+      </c>
+      <c r="B109" s="166" t="n"/>
+      <c r="C109" s="166" t="n"/>
+      <c r="D109" s="166" t="n"/>
+      <c r="E109" s="166" t="n"/>
+      <c r="F109" s="166" t="n"/>
+      <c r="G109" s="166" t="n"/>
+      <c r="H109" s="116" t="n"/>
+      <c r="I109" s="116" t="n"/>
+    </row>
+    <row r="110" ht="29" customHeight="1" s="67">
+      <c r="A110" s="116" t="n">
+        <v>96</v>
+      </c>
+      <c r="B110" s="166" t="n"/>
+      <c r="C110" s="166" t="n"/>
+      <c r="D110" s="166" t="n"/>
+      <c r="E110" s="166" t="n"/>
+      <c r="F110" s="166" t="n"/>
+      <c r="G110" s="166" t="n"/>
+      <c r="H110" s="116" t="n"/>
+      <c r="I110" s="116" t="n"/>
+    </row>
+    <row r="111" ht="29" customHeight="1" s="67">
+      <c r="A111" s="116" t="n">
+        <v>97</v>
+      </c>
+      <c r="B111" s="166" t="n"/>
+      <c r="C111" s="166" t="n"/>
+      <c r="D111" s="166" t="n"/>
+      <c r="E111" s="166" t="n"/>
+      <c r="F111" s="166" t="n"/>
+      <c r="G111" s="166" t="n"/>
+      <c r="H111" s="116" t="n"/>
+      <c r="I111" s="116" t="n"/>
+    </row>
+    <row r="112" ht="29" customHeight="1" s="67">
+      <c r="A112" s="116" t="n">
+        <v>98</v>
+      </c>
+      <c r="B112" s="166" t="n"/>
+      <c r="C112" s="166" t="n"/>
+      <c r="D112" s="166" t="n"/>
+      <c r="E112" s="166" t="n"/>
+      <c r="F112" s="166" t="n"/>
+      <c r="G112" s="166" t="n"/>
+      <c r="H112" s="116" t="n"/>
+      <c r="I112" s="116" t="n"/>
+    </row>
+    <row r="113" ht="29" customHeight="1" s="67">
+      <c r="A113" s="116" t="n">
+        <v>99</v>
+      </c>
+      <c r="B113" s="166" t="n"/>
+      <c r="C113" s="166" t="n"/>
+      <c r="D113" s="166" t="n"/>
+      <c r="E113" s="166" t="n"/>
+      <c r="F113" s="166" t="n"/>
+      <c r="G113" s="166" t="n"/>
+      <c r="H113" s="116" t="n"/>
+      <c r="I113" s="116" t="n"/>
+    </row>
+    <row r="114" ht="29" customHeight="1" s="67">
+      <c r="A114" s="116" t="n">
+        <v>100</v>
+      </c>
+      <c r="B114" s="166" t="n"/>
+      <c r="C114" s="166" t="n"/>
+      <c r="D114" s="166" t="n"/>
+      <c r="E114" s="166" t="n"/>
+      <c r="F114" s="166" t="n"/>
+      <c r="G114" s="166" t="n"/>
+      <c r="H114" s="116" t="n"/>
+      <c r="I114" s="116" t="n"/>
+    </row>
+    <row r="115" ht="29" customHeight="1" s="67">
+      <c r="A115" s="116" t="n">
+        <v>101</v>
+      </c>
+      <c r="B115" s="166" t="n"/>
+      <c r="C115" s="166" t="n"/>
+      <c r="D115" s="166" t="n"/>
+      <c r="E115" s="166" t="n"/>
+      <c r="F115" s="166" t="n"/>
+      <c r="G115" s="166" t="n"/>
+      <c r="H115" s="116" t="n"/>
+      <c r="I115" s="116" t="n"/>
+    </row>
+    <row r="116" ht="29" customHeight="1" s="67">
+      <c r="A116" s="116" t="n">
+        <v>102</v>
+      </c>
+      <c r="B116" s="166" t="n"/>
+      <c r="C116" s="166" t="n"/>
+      <c r="D116" s="166" t="n"/>
+      <c r="E116" s="166" t="n"/>
+      <c r="F116" s="166" t="n"/>
+      <c r="G116" s="166" t="n"/>
+      <c r="H116" s="116" t="n"/>
+      <c r="I116" s="116" t="n"/>
+    </row>
+    <row r="117" ht="29" customHeight="1" s="67">
+      <c r="A117" s="116" t="n">
+        <v>103</v>
+      </c>
+      <c r="B117" s="166" t="n"/>
+      <c r="C117" s="166" t="n"/>
+      <c r="D117" s="166" t="n"/>
+      <c r="E117" s="166" t="n"/>
+      <c r="F117" s="166" t="n"/>
+      <c r="G117" s="166" t="n"/>
+      <c r="H117" s="116" t="n"/>
+      <c r="I117" s="116" t="n"/>
+    </row>
+    <row r="118" ht="29" customHeight="1" s="67">
+      <c r="A118" s="116" t="n">
+        <v>104</v>
+      </c>
+      <c r="B118" s="166" t="n"/>
+      <c r="C118" s="166" t="n"/>
+      <c r="D118" s="166" t="n"/>
+      <c r="E118" s="166" t="n"/>
+      <c r="F118" s="166" t="n"/>
+      <c r="G118" s="166" t="n"/>
+      <c r="H118" s="116" t="n"/>
+      <c r="I118" s="116" t="n"/>
+    </row>
+    <row r="119" ht="29" customHeight="1" s="67">
+      <c r="A119" s="116" t="n">
+        <v>105</v>
+      </c>
+      <c r="B119" s="166" t="n"/>
+      <c r="C119" s="166" t="n"/>
+      <c r="D119" s="166" t="n"/>
+      <c r="E119" s="166" t="n"/>
+      <c r="F119" s="166" t="n"/>
+      <c r="G119" s="166" t="n"/>
+      <c r="H119" s="116" t="n"/>
+      <c r="I119" s="116" t="n"/>
+    </row>
+    <row r="120" ht="29" customHeight="1" s="67">
+      <c r="A120" s="116" t="n">
+        <v>106</v>
+      </c>
+      <c r="B120" s="166" t="n"/>
+      <c r="C120" s="166" t="n"/>
+      <c r="D120" s="166" t="n"/>
+      <c r="E120" s="166" t="n"/>
+      <c r="F120" s="166" t="n"/>
+      <c r="G120" s="166" t="n"/>
+      <c r="H120" s="116" t="n"/>
+      <c r="I120" s="116" t="n"/>
+    </row>
+    <row r="121" ht="29" customHeight="1" s="67">
+      <c r="A121" s="116" t="n">
+        <v>107</v>
+      </c>
+      <c r="B121" s="166" t="n"/>
+      <c r="C121" s="166" t="n"/>
+      <c r="D121" s="166" t="n"/>
+      <c r="E121" s="166" t="n"/>
+      <c r="F121" s="166" t="n"/>
+      <c r="G121" s="166" t="n"/>
+      <c r="H121" s="116" t="n"/>
+      <c r="I121" s="116" t="n"/>
+    </row>
+    <row r="122" ht="29" customHeight="1" s="67">
+      <c r="A122" s="116" t="n">
+        <v>108</v>
+      </c>
+      <c r="B122" s="166" t="n"/>
+      <c r="C122" s="166" t="n"/>
+      <c r="D122" s="166" t="n"/>
+      <c r="E122" s="166" t="n"/>
+      <c r="F122" s="166" t="n"/>
+      <c r="G122" s="166" t="n"/>
+      <c r="H122" s="116" t="n"/>
+      <c r="I122" s="116" t="n"/>
+    </row>
+    <row r="123" ht="29" customHeight="1" s="67">
+      <c r="A123" s="116" t="n">
+        <v>109</v>
+      </c>
+      <c r="B123" s="166" t="n"/>
+      <c r="C123" s="166" t="n"/>
+      <c r="D123" s="166" t="n"/>
+      <c r="E123" s="166" t="n"/>
+      <c r="F123" s="166" t="n"/>
+      <c r="G123" s="166" t="n"/>
+      <c r="H123" s="116" t="n"/>
+      <c r="I123" s="116" t="n"/>
+    </row>
+    <row r="124" ht="29" customHeight="1" s="67">
+      <c r="A124" s="116" t="n">
+        <v>110</v>
+      </c>
+      <c r="B124" s="166" t="n"/>
+      <c r="C124" s="166" t="n"/>
+      <c r="D124" s="166" t="n"/>
+      <c r="E124" s="166" t="n"/>
+      <c r="F124" s="166" t="n"/>
+      <c r="G124" s="166" t="n"/>
+      <c r="H124" s="116" t="n"/>
+      <c r="I124" s="116" t="n"/>
+    </row>
+    <row r="125" ht="29" customHeight="1" s="67">
+      <c r="A125" s="116" t="n">
+        <v>111</v>
+      </c>
+      <c r="B125" s="166" t="n"/>
+      <c r="C125" s="166" t="n"/>
+      <c r="D125" s="166" t="n"/>
+      <c r="E125" s="166" t="n"/>
+      <c r="F125" s="166" t="n"/>
+      <c r="G125" s="166" t="n"/>
+      <c r="H125" s="116" t="n"/>
+      <c r="I125" s="116" t="n"/>
+    </row>
+    <row r="126" ht="29" customHeight="1" s="67">
+      <c r="A126" s="116" t="n">
+        <v>112</v>
+      </c>
+      <c r="B126" s="166" t="n"/>
+      <c r="C126" s="166" t="n"/>
+      <c r="D126" s="166" t="n"/>
+      <c r="E126" s="166" t="n"/>
+      <c r="F126" s="166" t="n"/>
+      <c r="G126" s="166" t="n"/>
+      <c r="H126" s="116" t="n"/>
+      <c r="I126" s="116" t="n"/>
+    </row>
+    <row r="127" ht="29" customHeight="1" s="67">
+      <c r="A127" s="116" t="n">
+        <v>113</v>
+      </c>
+      <c r="B127" s="166" t="n"/>
+      <c r="C127" s="166" t="n"/>
+      <c r="D127" s="166" t="n"/>
+      <c r="E127" s="166" t="n"/>
+      <c r="F127" s="166" t="n"/>
+      <c r="G127" s="166" t="n"/>
+      <c r="H127" s="116" t="n"/>
+      <c r="I127" s="116" t="n"/>
+    </row>
+    <row r="128" ht="29" customHeight="1" s="67">
+      <c r="A128" s="116" t="n">
+        <v>114</v>
+      </c>
+      <c r="B128" s="166" t="n"/>
+      <c r="C128" s="166" t="n"/>
+      <c r="D128" s="166" t="n"/>
+      <c r="E128" s="166" t="n"/>
+      <c r="F128" s="166" t="n"/>
+      <c r="G128" s="166" t="n"/>
+      <c r="H128" s="116" t="n"/>
+      <c r="I128" s="116" t="n"/>
+    </row>
+    <row r="129" ht="29" customHeight="1" s="67">
+      <c r="A129" s="116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B129" s="166" t="n"/>
+      <c r="C129" s="166" t="n"/>
+      <c r="D129" s="166" t="n"/>
+      <c r="E129" s="166" t="n"/>
+      <c r="F129" s="166" t="n"/>
+      <c r="G129" s="166" t="n"/>
+      <c r="H129" s="116" t="n"/>
+      <c r="I129" s="116" t="n"/>
+    </row>
+    <row r="130" ht="29" customHeight="1" s="67">
+      <c r="A130" s="116" t="n">
+        <v>116</v>
+      </c>
+      <c r="B130" s="166" t="n"/>
+      <c r="C130" s="166" t="n"/>
+      <c r="D130" s="166" t="n"/>
+      <c r="E130" s="166" t="n"/>
+      <c r="F130" s="166" t="n"/>
+      <c r="G130" s="166" t="n"/>
+      <c r="H130" s="116" t="n"/>
+      <c r="I130" s="116" t="n"/>
+    </row>
+    <row r="131" ht="29" customHeight="1" s="67">
+      <c r="A131" s="116" t="n">
+        <v>117</v>
+      </c>
+      <c r="B131" s="166" t="n"/>
+      <c r="C131" s="166" t="n"/>
+      <c r="D131" s="166" t="n"/>
+      <c r="E131" s="166" t="n"/>
+      <c r="F131" s="166" t="n"/>
+      <c r="G131" s="166" t="n"/>
+      <c r="H131" s="116" t="n"/>
+      <c r="I131" s="116" t="n"/>
+    </row>
+    <row r="132" ht="29" customHeight="1" s="67">
+      <c r="A132" s="116" t="n">
+        <v>118</v>
+      </c>
+      <c r="B132" s="166" t="n"/>
+      <c r="C132" s="166" t="n"/>
+      <c r="D132" s="166" t="n"/>
+      <c r="E132" s="166" t="n"/>
+      <c r="F132" s="166" t="n"/>
+      <c r="G132" s="166" t="n"/>
+      <c r="H132" s="116" t="n"/>
+      <c r="I132" s="116" t="n"/>
+    </row>
+    <row r="133" ht="29" customHeight="1" s="67">
+      <c r="A133" s="116" t="n">
+        <v>119</v>
+      </c>
+      <c r="B133" s="166" t="n"/>
+      <c r="C133" s="166" t="n"/>
+      <c r="D133" s="166" t="n"/>
+      <c r="E133" s="166" t="n"/>
+      <c r="F133" s="166" t="n"/>
+      <c r="G133" s="166" t="n"/>
+      <c r="H133" s="116" t="n"/>
+      <c r="I133" s="116" t="n"/>
+    </row>
+    <row r="134" ht="29" customHeight="1" s="67">
+      <c r="A134" s="116" t="n">
+        <v>120</v>
+      </c>
+      <c r="B134" s="166" t="n"/>
+      <c r="C134" s="166" t="n"/>
+      <c r="D134" s="166" t="n"/>
+      <c r="E134" s="166" t="n"/>
+      <c r="F134" s="166" t="n"/>
+      <c r="G134" s="166" t="n"/>
+      <c r="H134" s="116" t="n"/>
+      <c r="I134" s="116" t="n"/>
+    </row>
+    <row r="135" ht="19.95" customHeight="1" s="67">
+      <c r="A135" s="108" t="inlineStr">
         <is>
           <t>Registros vigentes</t>
         </is>
       </c>
-      <c r="B34" s="31" t="n"/>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="32" t="n"/>
-      <c r="G34" s="119">
-        <f>COUNTIF(I15:I33,"Vigente")</f>
+      <c r="B135" s="31" t="n"/>
+      <c r="C135" s="31" t="n"/>
+      <c r="D135" s="31" t="n"/>
+      <c r="E135" s="31" t="n"/>
+      <c r="F135" s="32" t="n"/>
+      <c r="G135" s="119">
+        <f>COUNTIF(I15:I134,"Vigente")</f>
         <v/>
       </c>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="32" t="n"/>
+      <c r="H135" s="31" t="n"/>
+      <c r="I135" s="32" t="n"/>
     </row>
-    <row r="35" ht="19.95" customHeight="1" s="67">
-      <c r="A35" s="87" t="inlineStr">
+    <row r="136" ht="19.95" customHeight="1" s="67">
+      <c r="A136" s="87" t="inlineStr">
         <is>
           <t>Los tiempos de conservación y los lugares de archivo escritos son una propuesta: se ajustan a lo que exija el contrato, la interventoría y la política de la empresa.</t>
         </is>
       </c>
-      <c r="B35" s="31" t="n"/>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="32" t="n"/>
+      <c r="B136" s="31" t="n"/>
+      <c r="C136" s="31" t="n"/>
+      <c r="D136" s="31" t="n"/>
+      <c r="E136" s="31" t="n"/>
+      <c r="F136" s="31" t="n"/>
+      <c r="G136" s="31" t="n"/>
+      <c r="H136" s="31" t="n"/>
+      <c r="I136" s="32" t="n"/>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="67">
-      <c r="A36" s="77" t="inlineStr">
+    <row r="137" ht="16.5" customHeight="1" s="67">
+      <c r="A137" s="77" t="inlineStr">
         <is>
           <t>3. FIRMAS</t>
         </is>
       </c>
-      <c r="B36" s="31" t="n"/>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="32" t="n"/>
+      <c r="B137" s="31" t="n"/>
+      <c r="C137" s="31" t="n"/>
+      <c r="D137" s="31" t="n"/>
+      <c r="E137" s="31" t="n"/>
+      <c r="F137" s="31" t="n"/>
+      <c r="G137" s="31" t="n"/>
+      <c r="H137" s="31" t="n"/>
+      <c r="I137" s="32" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1" s="67">
-      <c r="A37" s="88" t="inlineStr">
+    <row r="138" ht="18" customHeight="1" s="67">
+      <c r="A138" s="88" t="inlineStr">
         <is>
           <t>ELABORÓ — INSPECTOR / INGENIERO DE CALIDAD</t>
         </is>
       </c>
-      <c r="B37" s="31" t="n"/>
-      <c r="C37" s="32" t="n"/>
-      <c r="D37" s="88" t="inlineStr">
+      <c r="B138" s="31" t="n"/>
+      <c r="C138" s="32" t="n"/>
+      <c r="D138" s="88" t="inlineStr">
         <is>
           <t>REVISÓ — RESIDENTE DE OBRA</t>
         </is>
       </c>
-      <c r="E37" s="31" t="n"/>
-      <c r="F37" s="32" t="n"/>
-      <c r="G37" s="88" t="inlineStr">
+      <c r="E138" s="31" t="n"/>
+      <c r="F138" s="32" t="n"/>
+      <c r="G138" s="88" t="inlineStr">
         <is>
           <t>Vo.Bo. — GERENCIA / INTERVENTORÍA</t>
         </is>
       </c>
-      <c r="H37" s="31" t="n"/>
-      <c r="I37" s="32" t="n"/>
+      <c r="H138" s="31" t="n"/>
+      <c r="I138" s="32" t="n"/>
     </row>
-    <row r="38" ht="42" customHeight="1" s="67">
-      <c r="A38" s="89" t="inlineStr">
+    <row r="139" ht="42" customHeight="1" s="67">
+      <c r="A139" s="89" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="B38" s="32" t="n"/>
-      <c r="C38" s="161" t="n"/>
-      <c r="D38" s="89" t="inlineStr">
+      <c r="B139" s="32" t="n"/>
+      <c r="C139" s="161" t="n"/>
+      <c r="D139" s="89" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="E38" s="32" t="n"/>
-      <c r="F38" s="161" t="n"/>
-      <c r="G38" s="89" t="inlineStr">
+      <c r="E139" s="32" t="n"/>
+      <c r="F139" s="161" t="n"/>
+      <c r="G139" s="89" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="H38" s="32" t="n"/>
-      <c r="I38" s="161" t="n"/>
+      <c r="H139" s="32" t="n"/>
+      <c r="I139" s="161" t="n"/>
     </row>
-    <row r="39" ht="21" customHeight="1" s="67">
-      <c r="A39" s="89" t="inlineStr">
+    <row r="140" ht="21" customHeight="1" s="67">
+      <c r="A140" s="89" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="B39" s="32" t="n"/>
-      <c r="C39" s="161" t="n"/>
-      <c r="D39" s="89" t="inlineStr">
+      <c r="B140" s="32" t="n"/>
+      <c r="C140" s="161" t="n"/>
+      <c r="D140" s="89" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="E39" s="32" t="n"/>
-      <c r="F39" s="161" t="n"/>
-      <c r="G39" s="89" t="inlineStr">
+      <c r="E140" s="32" t="n"/>
+      <c r="F140" s="161" t="n"/>
+      <c r="G140" s="89" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="H39" s="32" t="n"/>
-      <c r="I39" s="161" t="n"/>
+      <c r="H140" s="32" t="n"/>
+      <c r="I140" s="161" t="n"/>
     </row>
-    <row r="40" ht="21" customHeight="1" s="67">
-      <c r="A40" s="89" t="inlineStr">
+    <row r="141" ht="21" customHeight="1" s="67">
+      <c r="A141" s="89" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="B40" s="32" t="n"/>
-      <c r="C40" s="161" t="n"/>
-      <c r="D40" s="89" t="inlineStr">
+      <c r="B141" s="32" t="n"/>
+      <c r="C141" s="161" t="n"/>
+      <c r="D141" s="89" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="E40" s="32" t="n"/>
-      <c r="F40" s="161" t="n"/>
-      <c r="G40" s="89" t="inlineStr">
+      <c r="E141" s="32" t="n"/>
+      <c r="F141" s="161" t="n"/>
+      <c r="G141" s="89" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="H40" s="32" t="n"/>
-      <c r="I40" s="161" t="n"/>
+      <c r="H141" s="32" t="n"/>
+      <c r="I141" s="161" t="n"/>
     </row>
-    <row r="41" s="67">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="142" s="67">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>REV. 09/10/2026</t>
         </is>
       </c>
-      <c r="E41" s="33">
+      <c r="E142" s="33">
         <f>H5</f>
         <v/>
       </c>
@@ -12936,44 +14246,44 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="35">
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="A137:I137"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="E142:I142"/>
+    <mergeCell ref="A136:I136"/>
+    <mergeCell ref="D140:E140"/>
     <mergeCell ref="D1:I2"/>
+    <mergeCell ref="D139:E139"/>
     <mergeCell ref="H6:I6"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="G141:H141"/>
     <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="D141:E141"/>
     <mergeCell ref="D3:I3"/>
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="G135:I135"/>
+    <mergeCell ref="G138:I138"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A139:B139"/>
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="A10:I10"/>
+    <mergeCell ref="G139:H139"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="F12:I12"/>
     <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="E41:I41"/>
-    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="A141:B141"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="A140:B140"/>
+    <mergeCell ref="A138:C138"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="H8:I8"/>
-    <mergeCell ref="G40:H40"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="G140:H140"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.7" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 Página &amp;P de &amp;N</oddFooter>
